--- a/results/Int All Data -0.3/Linea_fi_explain.xlsx
+++ b/results/Int All Data -0.3/Linea_fi_explain.xlsx
@@ -1712,7 +1712,7 @@
         <v>0.0005253492810218076</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004478970120840914</v>
+        <v>0.004485293231811512</v>
       </c>
       <c r="O3" t="n">
         <v>-0.002193355383157899</v>
@@ -1763,7 +1763,7 @@
         <v>-0.003498839097061524</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.001943124817867397</v>
+        <v>0.001943147245556703</v>
       </c>
       <c r="AF3" t="n">
         <v>-0.001961861653119348</v>
@@ -1778,10 +1778,10 @@
         <v>-0.00101489183988606</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.013289273748967</v>
+        <v>0.01329584066823233</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.01914985401779326</v>
+        <v>0.01914668845907215</v>
       </c>
       <c r="AL3" t="n">
         <v>0.01053649251334581</v>
@@ -1802,7 +1802,7 @@
         <v>-0.002172493816965306</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.001943147245556703</v>
+        <v>0.001943124817867397</v>
       </c>
       <c r="AS3" t="n">
         <v>0.004665484460921717</v>
@@ -1856,7 +1856,7 @@
         <v>0.07650166443222742</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.009065719397081184</v>
+        <v>0.009068884955802301</v>
       </c>
       <c r="BK3" t="n">
         <v>0.06823271032268119</v>
@@ -1898,19 +1898,19 @@
         <v>0.000331516332734858</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.002999223037056894</v>
+        <v>0.002999390580566146</v>
       </c>
       <c r="BY3" t="n">
         <v>0.001085262687917228</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.001085262687917228</v>
+        <v>0.001088487454121677</v>
       </c>
       <c r="CA3" t="n">
         <v>0.0078962416129758</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0.005310895038307664</v>
+        <v>-0.005317303240806865</v>
       </c>
       <c r="CC3" t="n">
         <v>0.01324165240352842</v>
@@ -1922,7 +1922,7 @@
         <v>-0.0007055466883215611</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.001485991526251182</v>
+        <v>0.001485992422393646</v>
       </c>
       <c r="CG3" t="n">
         <v>0.3674885815538997</v>
@@ -1958,7 +1958,7 @@
         <v>0.05909995939593219</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.08257756624099361</v>
+        <v>0.0825807277964789</v>
       </c>
       <c r="CS3" t="n">
         <v>0.3018850051391381</v>
@@ -1976,7 +1976,7 @@
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.06042933209929686</v>
+        <v>0.06042612799804727</v>
       </c>
       <c r="CY3" t="n">
         <v>0.08009685720335344</v>
@@ -2181,7 +2181,7 @@
         <v>0.003391963113492831</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01206782970902819</v>
+        <v>0.0120720665868623</v>
       </c>
       <c r="O4" t="n">
         <v>0.00908583200557124</v>
@@ -2232,7 +2232,7 @@
         <v>0.006034029044954355</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.002106784104503656</v>
+        <v>0.002104873902635249</v>
       </c>
       <c r="AF4" t="n">
         <v>0.006056820480157858</v>
@@ -2247,10 +2247,10 @@
         <v>0.003308703941211718</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.02195275364085431</v>
+        <v>0.02195132625073267</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01780607387287037</v>
+        <v>0.01780326225326248</v>
       </c>
       <c r="AL4" t="n">
         <v>0.01763750003960332</v>
@@ -2271,7 +2271,7 @@
         <v>0.004875057751783609</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.002104873902635249</v>
+        <v>0.002106784104503656</v>
       </c>
       <c r="AS4" t="n">
         <v>0.01343652430956862</v>
@@ -2325,7 +2325,7 @@
         <v>0.04238387248057656</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.011601316841377</v>
+        <v>0.011599397827854</v>
       </c>
       <c r="BK4" t="n">
         <v>0.07671234929774814</v>
@@ -2367,19 +2367,19 @@
         <v>0.0004576544620120122</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.008413685857977301</v>
+        <v>0.008403044522318034</v>
       </c>
       <c r="BY4" t="n">
         <v>0.005930661967388597</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.005930661967388597</v>
+        <v>0.005925297804313986</v>
       </c>
       <c r="CA4" t="n">
         <v>0.01333811280435318</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.009666758521000617</v>
+        <v>0.009662819922870302</v>
       </c>
       <c r="CC4" t="n">
         <v>0.0290315680113091</v>
@@ -2391,7 +2391,7 @@
         <v>0.002529479180932136</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.004261129937006438</v>
+        <v>0.004260966672614601</v>
       </c>
       <c r="CG4" t="n">
         <v>0.0772284078877056</v>
@@ -2427,7 +2427,7 @@
         <v>0.02868937305666203</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.06818514778389786</v>
+        <v>0.06818490268332615</v>
       </c>
       <c r="CS4" t="n">
         <v>0.1106346629155278</v>
@@ -2445,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.04431397788893099</v>
+        <v>0.0443174076443731</v>
       </c>
       <c r="CY4" t="n">
         <v>0.04530424695019868</v>
@@ -2701,7 +2701,7 @@
         <v>-0.01617692545623258</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.0007689842999039187</v>
+        <v>-0.0007369432874079207</v>
       </c>
       <c r="AF5" t="n">
         <v>-0.01158129175946544</v>
@@ -2716,7 +2716,7 @@
         <v>-0.009338521400778177</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.02363945578231291</v>
+        <v>-0.02360544217687074</v>
       </c>
       <c r="AK5" t="n">
         <v>-0.001826337712271764</v>
@@ -2740,7 +2740,7 @@
         <v>-0.009417753738466383</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.0007369432874079207</v>
+        <v>-0.0007689842999039187</v>
       </c>
       <c r="AS5" t="n">
         <v>-0.01466751511294934</v>
@@ -2842,7 +2842,7 @@
         <v>-0.007803934214769414</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.007803934214769414</v>
+        <v>-0.007771686552724921</v>
       </c>
       <c r="CA5" t="n">
         <v>-0.0118775131456851</v>
@@ -3170,7 +3170,7 @@
         <v>-0.006050636148384195</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.0003883914367529163</v>
+        <v>0.0003645288850507189</v>
       </c>
       <c r="AF6" t="n">
         <v>-0.005964559256359738</v>
@@ -3209,7 +3209,7 @@
         <v>-0.005657285724818451</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.0003645288850507189</v>
+        <v>0.0003883914367529163</v>
       </c>
       <c r="AS6" t="n">
         <v>-0.003724996394528421</v>
@@ -3263,7 +3263,7 @@
         <v>0.05156896972401583</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.0009910058222697053</v>
+        <v>0.0009989197190724912</v>
       </c>
       <c r="BK6" t="n">
         <v>0.005742707587083176</v>
@@ -3305,7 +3305,7 @@
         <v>7.89925425608684e-05</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.001597982100221046</v>
+        <v>-0.001590078211507798</v>
       </c>
       <c r="BY6" t="n">
         <v>-0.001684941197102416</v>
@@ -3834,7 +3834,7 @@
         <v>0.05606129708301508</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.08610437694220148</v>
+        <v>0.08612018471962797</v>
       </c>
       <c r="CS7" t="n">
         <v>0.2828998858181737</v>
@@ -4057,7 +4057,7 @@
         <v>0.002927960409654093</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01132010995891989</v>
+        <v>0.01136753329119937</v>
       </c>
       <c r="O8" t="n">
         <v>0.004284820852601831</v>
@@ -4126,7 +4126,7 @@
         <v>0.02531604928425102</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.03043670493770292</v>
+        <v>0.03041296324729455</v>
       </c>
       <c r="AL8" t="n">
         <v>0.01382998116677326</v>
@@ -4255,7 +4255,7 @@
         <v>0.01889788944611071</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0.0002368387661563442</v>
+        <v>-0.0002849002849003413</v>
       </c>
       <c r="CC8" t="n">
         <v>0.009897990545758129</v>
@@ -4267,7 +4267,7 @@
         <v>0.0008424980804841664</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.001466723093770553</v>
+        <v>0.001451759754958801</v>
       </c>
       <c r="CG8" t="n">
         <v>0.4163028737607208</v>
@@ -4592,7 +4592,7 @@
         <v>0.002387774594078251</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.04403292181069954</v>
+        <v>0.04406457739791068</v>
       </c>
       <c r="AK9" t="n">
         <v>0.05276863214606409</v>
@@ -4712,7 +4712,7 @@
         <v>0.001017964071856248</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.02565868263473051</v>
+        <v>0.02562874251497004</v>
       </c>
       <c r="BY9" t="n">
         <v>0.01473886574815759</v>
